--- a/public/files/farmers.xlsx
+++ b/public/files/farmers.xlsx
@@ -5,19 +5,22 @@
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Sheet5" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataSignature="AMtx7miC76s4LDCi9+5Tqa4Xl3iuhdoMtQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mjRprWbBx/1Cb7y4nYpt/NJq0OK1w=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="491">
   <si>
     <t>name</t>
   </si>
@@ -626,13 +629,877 @@
   </si>
   <si>
     <t>Ishmael Sama</t>
+  </si>
+  <si>
+    <t>Jibril Adamu</t>
+  </si>
+  <si>
+    <t>Fatima Wakili</t>
+  </si>
+  <si>
+    <t>Umar Jauro</t>
+  </si>
+  <si>
+    <t>Adamu UsmanGuli</t>
+  </si>
+  <si>
+    <t>Yahaya Bomala</t>
+  </si>
+  <si>
+    <t>Abubakar Bashir</t>
+  </si>
+  <si>
+    <t>Mustapha Abubakar</t>
+  </si>
+  <si>
+    <t>Adamu Abdullaih</t>
+  </si>
+  <si>
+    <t>Madaki Mustapha</t>
+  </si>
+  <si>
+    <t>Zarau Mustapha</t>
+  </si>
+  <si>
+    <t>Abdu Bello</t>
+  </si>
+  <si>
+    <t>Dauda Muktar</t>
+  </si>
+  <si>
+    <t>DahiruAhmad Chiroma</t>
+  </si>
+  <si>
+    <t>Salisu Jibrin</t>
+  </si>
+  <si>
+    <t>Sulaiman Abdulmumini</t>
+  </si>
+  <si>
+    <t>Alhaji Muhammad</t>
+  </si>
+  <si>
+    <t>Abdullahi Manu</t>
+  </si>
+  <si>
+    <t>Sadik Muhammadkala</t>
+  </si>
+  <si>
+    <t>Kabiru LamuwaMuhammad</t>
+  </si>
+  <si>
+    <t>Muhammad Aisami</t>
+  </si>
+  <si>
+    <t>Sani Madaki</t>
+  </si>
+  <si>
+    <t>Yakubu MohammedDukku</t>
+  </si>
+  <si>
+    <t>Buba Jibril</t>
+  </si>
+  <si>
+    <t>Adamu Abdullahi</t>
+  </si>
+  <si>
+    <t>Ahmed Bako</t>
+  </si>
+  <si>
+    <t>Yohanna Philip</t>
+  </si>
+  <si>
+    <t>Zakari Yerima</t>
+  </si>
+  <si>
+    <t>Muhammad Aliko</t>
+  </si>
+  <si>
+    <t>Barwuro Ibrahim</t>
+  </si>
+  <si>
+    <t>Abba Umar</t>
+  </si>
+  <si>
+    <t>Dauda Bzigu</t>
+  </si>
+  <si>
+    <t>Mustapha Yakubu</t>
+  </si>
+  <si>
+    <t>Salihu Zarami</t>
+  </si>
+  <si>
+    <t>Adamu Hassan</t>
+  </si>
+  <si>
+    <t>Sulaiman Liman</t>
+  </si>
+  <si>
+    <t>Ibrahim Umoru</t>
+  </si>
+  <si>
+    <t>LUCY ILIYA</t>
+  </si>
+  <si>
+    <t>Muhammad Abubakar</t>
+  </si>
+  <si>
+    <t>Martina Ayuba</t>
+  </si>
+  <si>
+    <t>Ibrahim Inuwa</t>
+  </si>
+  <si>
+    <t>Ibrahim Majidadi</t>
+  </si>
+  <si>
+    <t>Ali Muhammadu</t>
+  </si>
+  <si>
+    <t>Aisha Bello</t>
+  </si>
+  <si>
+    <t>Muazu Mohammed</t>
+  </si>
+  <si>
+    <t>Kyari Alhaji</t>
+  </si>
+  <si>
+    <t>Zungoma Mohammad</t>
+  </si>
+  <si>
+    <t>Jauro Babaradde</t>
+  </si>
+  <si>
+    <t>Adamu Isa</t>
+  </si>
+  <si>
+    <t>Ibrahim Adamu</t>
+  </si>
+  <si>
+    <t>Miss Amadu</t>
+  </si>
+  <si>
+    <t>Kawa Chiroma</t>
+  </si>
+  <si>
+    <t>Mohammed Idi</t>
+  </si>
+  <si>
+    <t>Jala Jauro</t>
+  </si>
+  <si>
+    <t>Babayo Ali</t>
+  </si>
+  <si>
+    <t>Fatu Danlaso</t>
+  </si>
+  <si>
+    <t>Rilwan Idris</t>
+  </si>
+  <si>
+    <t>Yahaya Abubakar</t>
+  </si>
+  <si>
+    <t>Usman Abubakar</t>
+  </si>
+  <si>
+    <t>Salihu Ibrahim</t>
+  </si>
+  <si>
+    <t>Muhammad Adamu</t>
+  </si>
+  <si>
+    <t>Waruba Zachary</t>
+  </si>
+  <si>
+    <t>Hassan Mahammadu</t>
+  </si>
+  <si>
+    <t>Hargom Umoru</t>
+  </si>
+  <si>
+    <t>Yahaya Usman</t>
+  </si>
+  <si>
+    <t>Umar HarunaManga</t>
+  </si>
+  <si>
+    <t>Chiroma Mustapha</t>
+  </si>
+  <si>
+    <t>Babangida Hassan</t>
+  </si>
+  <si>
+    <t>Mustapha Ali</t>
+  </si>
+  <si>
+    <t>Sekhar Rao</t>
+  </si>
+  <si>
+    <t>07800003034</t>
+  </si>
+  <si>
+    <t>Ibrahim Yakubu</t>
+  </si>
+  <si>
+    <t>Muhammadu Mustapha</t>
+  </si>
+  <si>
+    <t>Kawu Aliyu</t>
+  </si>
+  <si>
+    <t>Abdul Hammadu</t>
+  </si>
+  <si>
+    <t>Ziyada Ahmed</t>
+  </si>
+  <si>
+    <t>SARAH DAUMA</t>
+  </si>
+  <si>
+    <t>CHRISTOHPHER DANIEL</t>
+  </si>
+  <si>
+    <t>Musa Chiroma</t>
+  </si>
+  <si>
+    <t>Bala Sabo</t>
+  </si>
+  <si>
+    <t>Ibrahim Hamman</t>
+  </si>
+  <si>
+    <t>Bala Adamumuhammed</t>
+  </si>
+  <si>
+    <t>ILIYA LAMIDO</t>
+  </si>
+  <si>
+    <t>Rabiu Wakili</t>
+  </si>
+  <si>
+    <t>Jungudo ARasheed</t>
+  </si>
+  <si>
+    <t>Babayo Bappah</t>
+  </si>
+  <si>
+    <t>Ahmed Abubakar</t>
+  </si>
+  <si>
+    <t>Audu Mohammed</t>
+  </si>
+  <si>
+    <t>Mahdi Yahaya</t>
+  </si>
+  <si>
+    <t>Musa Yarima</t>
+  </si>
+  <si>
+    <t>Mariya Adamu</t>
+  </si>
+  <si>
+    <t>Sani Umaru</t>
+  </si>
+  <si>
+    <t>Abba Isaid</t>
+  </si>
+  <si>
+    <t>Abdullahi Maigari</t>
+  </si>
+  <si>
+    <t>Mauludu Mijinyawa</t>
+  </si>
+  <si>
+    <t>Aminu Muhammad</t>
+  </si>
+  <si>
+    <t>Umar Adamu</t>
+  </si>
+  <si>
+    <t>Abubakar Muhammadu</t>
+  </si>
+  <si>
+    <t>Yadima Abafaras</t>
+  </si>
+  <si>
+    <t>Mustapha Bukar</t>
+  </si>
+  <si>
+    <t>Mohammadu Dagachi</t>
+  </si>
+  <si>
+    <t>Buba Mohammed</t>
+  </si>
+  <si>
+    <t>Susana Emmanuel</t>
+  </si>
+  <si>
+    <t>Mohammad Madaja</t>
+  </si>
+  <si>
+    <t>ILIYA BITRUS</t>
+  </si>
+  <si>
+    <t>Habiba Saleh</t>
+  </si>
+  <si>
+    <t>Aishayu IbrahimShuaibu</t>
+  </si>
+  <si>
+    <t>Halilu Musa</t>
+  </si>
+  <si>
+    <t>Abdulhamid Abubakar</t>
+  </si>
+  <si>
+    <t>Abdurahman Abdullahi</t>
+  </si>
+  <si>
+    <t>Ibrahim Garba</t>
+  </si>
+  <si>
+    <t>Inuwa Umaru</t>
+  </si>
+  <si>
+    <t>Tijjani Jouro</t>
+  </si>
+  <si>
+    <t>Abubakar Ibrahim</t>
+  </si>
+  <si>
+    <t>Nasiru Yahya</t>
+  </si>
+  <si>
+    <t>Adamu MuhammadZaune</t>
+  </si>
+  <si>
+    <t>Sardauna Kawu</t>
+  </si>
+  <si>
+    <t>Bose MuminiAjiya</t>
+  </si>
+  <si>
+    <t>Muhammed Abba</t>
+  </si>
+  <si>
+    <t>Elijah Mary</t>
+  </si>
+  <si>
+    <t>Usman Babaaish</t>
+  </si>
+  <si>
+    <t>DAVID BINDOW</t>
+  </si>
+  <si>
+    <t>Linda Tumba</t>
+  </si>
+  <si>
+    <t>Shuaibu Yakubu</t>
+  </si>
+  <si>
+    <t>Kawu Mohammed</t>
+  </si>
+  <si>
+    <t>Ahmadu Hassan</t>
+  </si>
+  <si>
+    <t>Dahiru Muhammad</t>
+  </si>
+  <si>
+    <t>Muhammed Musa</t>
+  </si>
+  <si>
+    <t>Umar Sabiu</t>
+  </si>
+  <si>
+    <t>Mohammed Baba</t>
+  </si>
+  <si>
+    <t>Mubarak Ibrahim</t>
+  </si>
+  <si>
+    <t>Audu Bako</t>
+  </si>
+  <si>
+    <t>Ibrahim Ishaq</t>
+  </si>
+  <si>
+    <t>Umar Bawuro</t>
+  </si>
+  <si>
+    <t>Usman Aliyu</t>
+  </si>
+  <si>
+    <t>Jalige Zubairu</t>
+  </si>
+  <si>
+    <t>RukayyaYatu Hammantukur</t>
+  </si>
+  <si>
+    <t>Shayyabu Abubakar</t>
+  </si>
+  <si>
+    <t>Sunday Daniel</t>
+  </si>
+  <si>
+    <t>Abdulhamid Abdullahi</t>
+  </si>
+  <si>
+    <t>Kabiru Adamu</t>
+  </si>
+  <si>
+    <t>Samuel Ambrose</t>
+  </si>
+  <si>
+    <t>Muhammad Chiroma</t>
+  </si>
+  <si>
+    <t>Yarima Zango</t>
+  </si>
+  <si>
+    <t>Hussaini Musayaute</t>
+  </si>
+  <si>
+    <t>Lassa Tumba</t>
+  </si>
+  <si>
+    <t>Jaafar Abubakar</t>
+  </si>
+  <si>
+    <t>BintaA Ali</t>
+  </si>
+  <si>
+    <t>Mohammed Garba</t>
+  </si>
+  <si>
+    <t>Mohammed Nuhu</t>
+  </si>
+  <si>
+    <t>Sabiu Haladu</t>
+  </si>
+  <si>
+    <t>Dakasala Licksam</t>
+  </si>
+  <si>
+    <t>Umaru HammaduSuka</t>
+  </si>
+  <si>
+    <t>Bello Halilu</t>
+  </si>
+  <si>
+    <t>Umar Yahaya</t>
+  </si>
+  <si>
+    <t>Yarima Bar</t>
+  </si>
+  <si>
+    <t>Abubakar UsmanGuli</t>
+  </si>
+  <si>
+    <t>Saadu MohammadT</t>
+  </si>
+  <si>
+    <t>Ahmad Umar</t>
+  </si>
+  <si>
+    <t>Bafantami Hassan</t>
+  </si>
+  <si>
+    <t>Haruna Adamu</t>
+  </si>
+  <si>
+    <t>Hajja Rukayya</t>
+  </si>
+  <si>
+    <t>Shuaibu Adamu</t>
+  </si>
+  <si>
+    <t>Hamman Bulus</t>
+  </si>
+  <si>
+    <t>NafisaIsa Abubakar</t>
+  </si>
+  <si>
+    <t>Mohammed Ahmad</t>
+  </si>
+  <si>
+    <t>Amina Mahmud</t>
+  </si>
+  <si>
+    <t>Abdullahi Ibrahim</t>
+  </si>
+  <si>
+    <t>Jennifer OzigoObioma</t>
+  </si>
+  <si>
+    <t>Maigadu Maigari</t>
+  </si>
+  <si>
+    <t>Bubakari Babayo</t>
+  </si>
+  <si>
+    <t>Auwal AliHada</t>
+  </si>
+  <si>
+    <t>Barde AdamuDambaDukku</t>
+  </si>
+  <si>
+    <t>Adamu Sulaiman</t>
+  </si>
+  <si>
+    <t>Timothy Akuma</t>
+  </si>
+  <si>
+    <t>Zulaiharu Usman</t>
+  </si>
+  <si>
+    <t>Ahmed Mohammed</t>
+  </si>
+  <si>
+    <t>Aminu IdrisMuhammad</t>
+  </si>
+  <si>
+    <t>Samson Mallo</t>
+  </si>
+  <si>
+    <t>Auwal AdamuGamo</t>
+  </si>
+  <si>
+    <t>Bakoji Isa</t>
+  </si>
+  <si>
+    <t>Abubakar Usman</t>
+  </si>
+  <si>
+    <t>Aliyu MaiAnguwa</t>
+  </si>
+  <si>
+    <t>Wabiya Moses</t>
+  </si>
+  <si>
+    <t>Abubakar Abdul</t>
+  </si>
+  <si>
+    <t>Hassan Bakari</t>
+  </si>
+  <si>
+    <t>Zainab Ismail</t>
+  </si>
+  <si>
+    <t>Adamu Manu</t>
+  </si>
+  <si>
+    <t>Muhammad Hassan</t>
+  </si>
+  <si>
+    <t>Salisu Abdulrahman</t>
+  </si>
+  <si>
+    <t>Mohammed Hussaini</t>
+  </si>
+  <si>
+    <t>Mercy Medugu</t>
+  </si>
+  <si>
+    <t>Ahmed MuhammadAbubakar</t>
+  </si>
+  <si>
+    <t>Umar Hilu</t>
+  </si>
+  <si>
+    <t>Adamu DanAzumi</t>
+  </si>
+  <si>
+    <t>Chukwudi PeterAnakor</t>
+  </si>
+  <si>
+    <t>BAMAGA HAMMAJODA</t>
+  </si>
+  <si>
+    <t>Musa AbdullahiSambo</t>
+  </si>
+  <si>
+    <t>Mohammed Hashimu</t>
+  </si>
+  <si>
+    <t>Adamu Dauda</t>
+  </si>
+  <si>
+    <t>Jocop David</t>
+  </si>
+  <si>
+    <t>Julius Kennedy</t>
+  </si>
+  <si>
+    <t>Saidu Sani</t>
+  </si>
+  <si>
+    <t>Adamu Misa</t>
+  </si>
+  <si>
+    <t>Dahiru Alim</t>
+  </si>
+  <si>
+    <t>Iliya Hasssan</t>
+  </si>
+  <si>
+    <t>Haruna Rabiu</t>
+  </si>
+  <si>
+    <t>Abubakar Bapetel</t>
+  </si>
+  <si>
+    <t>Ishaku Umar</t>
+  </si>
+  <si>
+    <t>Bello Adamu</t>
+  </si>
+  <si>
+    <t>Aliyu Lawan</t>
+  </si>
+  <si>
+    <t>Abdulrahman Alhajiisa</t>
+  </si>
+  <si>
+    <t>Tarri Drambi</t>
+  </si>
+  <si>
+    <t>Hassan Misa</t>
+  </si>
+  <si>
+    <t>Saminu Usman</t>
+  </si>
+  <si>
+    <t>Abigail AhmedTwan</t>
+  </si>
+  <si>
+    <t>Tangawa Yakubu</t>
+  </si>
+  <si>
+    <t>Rahilla Yirau</t>
+  </si>
+  <si>
+    <t>Abbas Ayusuf</t>
+  </si>
+  <si>
+    <t>Ayuba Saadu</t>
+  </si>
+  <si>
+    <t>Adamu Mohammed</t>
+  </si>
+  <si>
+    <t>Saidu IdrisMakama</t>
+  </si>
+  <si>
+    <t>Shehu Jauro</t>
+  </si>
+  <si>
+    <t>Shuaibu Bala</t>
+  </si>
+  <si>
+    <t>Kabiru Sale</t>
+  </si>
+  <si>
+    <t>Muhammed Muhammed</t>
+  </si>
+  <si>
+    <t>Musa Yahaya</t>
+  </si>
+  <si>
+    <t>Milka Philimon</t>
+  </si>
+  <si>
+    <t>Salisu Hammayo</t>
+  </si>
+  <si>
+    <t>Jumma Abubakar</t>
+  </si>
+  <si>
+    <t>Julde Messa</t>
+  </si>
+  <si>
+    <t>Maigari Khalid</t>
+  </si>
+  <si>
+    <t>Husaini Magaji</t>
+  </si>
+  <si>
+    <t>Hassan Umaru</t>
+  </si>
+  <si>
+    <t>Hauwa Salihu</t>
+  </si>
+  <si>
+    <t>IMAILEY MOSES</t>
+  </si>
+  <si>
+    <t>Abba Mohammed</t>
+  </si>
+  <si>
+    <t>Abubakar Yuguda</t>
+  </si>
+  <si>
+    <t>Usman Babayo</t>
+  </si>
+  <si>
+    <t>Ibrahim Hussaini</t>
+  </si>
+  <si>
+    <t>Susuti Mathias</t>
+  </si>
+  <si>
+    <t>Samaila Muhammad</t>
+  </si>
+  <si>
+    <t>Muhammad Ibrahim</t>
+  </si>
+  <si>
+    <t>Lawiza Idris</t>
+  </si>
+  <si>
+    <t>Lauratu Ibrahim</t>
+  </si>
+  <si>
+    <t>Rifkatu Zira</t>
+  </si>
+  <si>
+    <t>Zulai Ibrahim</t>
+  </si>
+  <si>
+    <t>Abulkareem Aliyu</t>
+  </si>
+  <si>
+    <t>Buba Ibrahim</t>
+  </si>
+  <si>
+    <t>Baba Mallum</t>
+  </si>
+  <si>
+    <t>Phenuel Chama</t>
+  </si>
+  <si>
+    <t>Buba AhmaduDamba</t>
+  </si>
+  <si>
+    <t>Salihu Adamu</t>
+  </si>
+  <si>
+    <t>Abdulladif ABUBAKARIbrahim</t>
+  </si>
+  <si>
+    <t>Mercy Godwin</t>
+  </si>
+  <si>
+    <t>Joseph John</t>
+  </si>
+  <si>
+    <t>Hussaini Zarami</t>
+  </si>
+  <si>
+    <t>Abdullahi Abubakar</t>
+  </si>
+  <si>
+    <t>Usman Yarima</t>
+  </si>
+  <si>
+    <t>Halliru Sani</t>
+  </si>
+  <si>
+    <t>Mustapha Isah</t>
+  </si>
+  <si>
+    <t>Bello Babawuro</t>
+  </si>
+  <si>
+    <t>Musa Kawu</t>
+  </si>
+  <si>
+    <t>Ussah Bitrus</t>
+  </si>
+  <si>
+    <t>Ibrahim Hamidu</t>
+  </si>
+  <si>
+    <t>Jaafaru Mohammed</t>
+  </si>
+  <si>
+    <t>Dauda Umar</t>
+  </si>
+  <si>
+    <t>Adamu Chiroma</t>
+  </si>
+  <si>
+    <t>Yunusa Magaji</t>
+  </si>
+  <si>
+    <t>Yau Tukur</t>
+  </si>
+  <si>
+    <t>Muhammad Ajuji</t>
+  </si>
+  <si>
+    <t>Hassan Adamu</t>
+  </si>
+  <si>
+    <t>Bedia Simon</t>
+  </si>
+  <si>
+    <t>Mohammed Mustapha</t>
+  </si>
+  <si>
+    <t>Mary John</t>
+  </si>
+  <si>
+    <t>Zainab Bashir</t>
+  </si>
+  <si>
+    <t>DahiruUmar Drunkwa</t>
+  </si>
+  <si>
+    <t>Mohammed Abdulkadir</t>
+  </si>
+  <si>
+    <t>Ahmed Haladu</t>
+  </si>
+  <si>
+    <t>Mohammed Fulata</t>
+  </si>
+  <si>
+    <t>Umaru Sani</t>
+  </si>
+  <si>
+    <t>Ibrahim Samaila</t>
+  </si>
+  <si>
+    <t>Zubairu Yakubu</t>
+  </si>
+  <si>
+    <t>Garba Baba</t>
+  </si>
+  <si>
+    <t>Hassan Muhammad</t>
+  </si>
+  <si>
+    <t>Umaru Muhammadu</t>
+  </si>
+  <si>
+    <t>Leo Peter</t>
+  </si>
+  <si>
+    <t>Kabiru Yahaya</t>
+  </si>
+  <si>
+    <t>Dan Ibrahim</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -653,6 +1520,12 @@
     <font>
       <sz val="11.0"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -684,7 +1557,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -708,6 +1581,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="1" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -721,6 +1597,18 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -8140,4 +9028,5547 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <v>7.06663268E9</v>
+      </c>
+      <c r="E2" s="4" t="str">
+        <f t="shared" ref="E2:E73" si="1">TEXT(D2,"00000000000")</f>
+        <v>07066632680</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>7.066659376E9</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07066659376</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.066721813E9</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07066721813</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.066884991E9</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07066884991</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.066974947E9</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07066974947</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.067078292E9</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067078292</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.067167089E9</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067167089</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7.067199677E9</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067199677</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.067246088E9</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067246088</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.067408737E9</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067408737</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7.06752919E9</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067529190</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.067582029E9</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067582029</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7.067609353E9</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067609353</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.067646639E9</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07067646639</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>7.068178527E9</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068178527</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>7.068180898E9</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068180898</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3">
+        <v>7.068182468E9</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068182468</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>7.068223484E9</v>
+      </c>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068223484</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>7.068261035E9</v>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068261035</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3">
+        <v>7.068732723E9</v>
+      </c>
+      <c r="E21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068732723</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3">
+        <v>7.068799285E9</v>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068799285</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>7.068802185E9</v>
+      </c>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07068802185</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="3">
+        <v>7.069059671E9</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069059671</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>7.069207022E9</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069207022</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>7.069266056E9</v>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069266056</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>7.069634996E9</v>
+      </c>
+      <c r="E27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069634996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.069773213E9</v>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069773213</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>7.069773875E9</v>
+      </c>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07069773875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>7.070255511E9</v>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07070255511</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.075625622E9</v>
+      </c>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07075625622</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3">
+        <v>7.080046003E9</v>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07080046003</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
+        <v>7.080292642E9</v>
+      </c>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07080292642</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3">
+        <v>7.081305336E9</v>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07081305336</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>7.081381471E9</v>
+      </c>
+      <c r="E35" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07081381471</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3">
+        <v>7.081650948E9</v>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07081650948</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3">
+        <v>7.081773668E9</v>
+      </c>
+      <c r="E37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07081773668</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="3">
+        <v>7.082003651E9</v>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07082003651</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="3">
+        <v>7.082699145E9</v>
+      </c>
+      <c r="E39" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07082699145</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="3">
+        <v>7.083351131E9</v>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07083351131</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3">
+        <v>7.083447433E9</v>
+      </c>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07083447433</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3">
+        <v>7.083931504E9</v>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07083931504</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3">
+        <v>7.084383863E9</v>
+      </c>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084383863</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="3">
+        <v>7.084575662E9</v>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084575662</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="3">
+        <v>7.084908971E9</v>
+      </c>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084908971</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="3">
+        <v>7.084910131E9</v>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084910131</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3">
+        <v>7.084943431E9</v>
+      </c>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084943431</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>7.08498184E9</v>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07084981840</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="3">
+        <v>7.085174876E9</v>
+      </c>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07085174876</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3">
+        <v>7.085612065E9</v>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07085612065</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="3">
+        <v>7.08583737E9</v>
+      </c>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07085837370</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3">
+        <v>7.086194052E9</v>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086194052</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="3">
+        <v>7.086367715E9</v>
+      </c>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086367715</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3">
+        <v>7.086368173E9</v>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086368173</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="3">
+        <v>7.086422935E9</v>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086422935</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>7.086592685E9</v>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086592685</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>7.08664399E9</v>
+      </c>
+      <c r="E57" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086643990</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>7.086870883E9</v>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07086870883</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>7.087169593E9</v>
+      </c>
+      <c r="E59" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07087169593</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3">
+        <v>7.087261454E9</v>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07087261454</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3">
+        <v>7.087312227E9</v>
+      </c>
+      <c r="E61" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07087312227</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3">
+        <v>7.08830447E9</v>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07088304470</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>7.088511549E9</v>
+      </c>
+      <c r="E63" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07088511549</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3">
+        <v>7.08884553E9</v>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07088845530</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3">
+        <v>7.088849478E9</v>
+      </c>
+      <c r="E65" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07088849478</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3">
+        <v>7.089008354E9</v>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089008354</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="3">
+        <v>7.089028139E9</v>
+      </c>
+      <c r="E67" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089028139</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>7.089177374E9</v>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089177374</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3">
+        <v>7.089197397E9</v>
+      </c>
+      <c r="E69" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089197397</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="3">
+        <v>7.089237152E9</v>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089237152</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3">
+        <v>7.089237157E9</v>
+      </c>
+      <c r="E71" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089237157</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="3">
+        <v>7.089702652E9</v>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089702652</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="3">
+        <v>7.089760749E9</v>
+      </c>
+      <c r="E73" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>07089760749</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="6">
+        <v>7.800003034E9</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="3">
+        <v>7.935454534E9</v>
+      </c>
+      <c r="E75" s="4" t="str">
+        <f t="shared" ref="E75:E102" si="2">TEXT(D75,"00000000000")</f>
+        <v>07935454534</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="3">
+        <v>8.001104701E9</v>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08001104701</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="3">
+        <v>8.001135519E9</v>
+      </c>
+      <c r="E77" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08001135519</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="3">
+        <v>8.003740028E9</v>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08003740028</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="3">
+        <v>8.013845944E9</v>
+      </c>
+      <c r="E79" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08013845944</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="3">
+        <v>8.02080625E9</v>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08020806250</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="3">
+        <v>8.020806256E9</v>
+      </c>
+      <c r="E81" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08020806256</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="3">
+        <v>8.02119144E9</v>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08021191440</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8.02126266E9</v>
+      </c>
+      <c r="E83" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08021262660</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="3">
+        <v>8.021326277E9</v>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08021326277</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="3">
+        <v>8.022608875E9</v>
+      </c>
+      <c r="E85" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08022608875</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8.022738444E9</v>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08022738444</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="3">
+        <v>8.023113532E9</v>
+      </c>
+      <c r="E87" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023113532</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="3">
+        <v>8.023127384E9</v>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023127384</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="3">
+        <v>8.023132061E9</v>
+      </c>
+      <c r="E89" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023132061</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="3">
+        <v>8.023331313E9</v>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023331313</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="3">
+        <v>8.023454234E9</v>
+      </c>
+      <c r="E91" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023454234</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="3">
+        <v>8.023459281E9</v>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023459281</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="3">
+        <v>8.023695216E9</v>
+      </c>
+      <c r="E93" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023695216</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="3">
+        <v>8.023716593E9</v>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023716593</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="3">
+        <v>8.023903414E9</v>
+      </c>
+      <c r="E95" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08023903414</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="3">
+        <v>8.024191368E9</v>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024191368</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="3">
+        <v>8.024401001E9</v>
+      </c>
+      <c r="E97" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024401001</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="3">
+        <v>8.024471754E9</v>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024471754</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="3">
+        <v>8.024505961E9</v>
+      </c>
+      <c r="E99" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024505961</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="3">
+        <v>8.024542927E9</v>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024542927</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3">
+        <v>8.024599699E9</v>
+      </c>
+      <c r="E101" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024599699</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="3">
+        <v>8.024817602E9</v>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>08024817602</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B74"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <v>8.024937477E9</v>
+      </c>
+      <c r="E2" s="4" t="str">
+        <f t="shared" ref="E2:E102" si="1">TEXT(D2,"00000000000")</f>
+        <v>08024937477</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.025075767E9</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025075767</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8.025240267E9</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025240267</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.025516102E9</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025516102</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.025517367E9</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025517367</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.025601538E9</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025601538</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.025929986E9</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08025929986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.026063622E9</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08026063622</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.026596175E9</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08026596175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8.026605796E9</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08026605796</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.026768707E9</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08026768707</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.0269032E9</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08026903200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.027691563E9</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08027691563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.02791166E9</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08027911660</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.028283691E9</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028283691</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.028354335E9</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028354335</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8.028492152E9</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028492152</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8.028496291E9</v>
+      </c>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028496291</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8.028686648E9</v>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028686648</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.028811621E9</v>
+      </c>
+      <c r="E21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028811621</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8.028833952E9</v>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028833952</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8.028887131E9</v>
+      </c>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08028887131</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>8.029187666E9</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08029187666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>8.029335616E9</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08029335616</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8.029687016E9</v>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08029687016</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.03034441E9</v>
+      </c>
+      <c r="E27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030344410</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>8.030477852E9</v>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030477852</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8.030728454E9</v>
+      </c>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030728454</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>8.030804569E9</v>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030804569</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>8.030898352E9</v>
+      </c>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030898352</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.030922238E9</v>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08030922238</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
+        <v>8.031148514E9</v>
+      </c>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031148514</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3">
+        <v>8.03119343E9</v>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031193430</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>8.031316417E9</v>
+      </c>
+      <c r="E35" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031316417</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3">
+        <v>8.031319081E9</v>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031319081</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3">
+        <v>8.031569855E9</v>
+      </c>
+      <c r="E37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031569855</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="3">
+        <v>8.031941112E9</v>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08031941112</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="3">
+        <v>8.032169766E9</v>
+      </c>
+      <c r="E39" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032169766</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8.032554781E9</v>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032554781</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3">
+        <v>8.032598864E9</v>
+      </c>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032598864</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8.032632856E9</v>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032632856</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8.032682598E9</v>
+      </c>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032682598</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="3">
+        <v>8.032728052E9</v>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032728052</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="3">
+        <v>8.03280338E9</v>
+      </c>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032803380</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="3">
+        <v>8.032831468E9</v>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032831468</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8.032902737E9</v>
+      </c>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032902737</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="3">
+        <v>8.0329546E9</v>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08032954600</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="3">
+        <v>8.03300274E9</v>
+      </c>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08033002740</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3">
+        <v>8.033627947E9</v>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08033627947</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="3">
+        <v>8.033931315E9</v>
+      </c>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08033931315</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3">
+        <v>8.034163039E9</v>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034163039</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="3">
+        <v>8.034342869E9</v>
+      </c>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034342869</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3">
+        <v>8.034443044E9</v>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034443044</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="3">
+        <v>8.034812837E9</v>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034812837</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>8.034827381E9</v>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034827381</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>8.034955344E9</v>
+      </c>
+      <c r="E57" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08034955344</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>8.03509431E9</v>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035094310</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>8.035243882E9</v>
+      </c>
+      <c r="E59" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035243882</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3">
+        <v>8.035258994E9</v>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035258994</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3">
+        <v>8.035357021E9</v>
+      </c>
+      <c r="E61" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035357021</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3">
+        <v>8.035367395E9</v>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035367395</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>8.035416051E9</v>
+      </c>
+      <c r="E63" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035416051</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3">
+        <v>8.035591744E9</v>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035591744</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3">
+        <v>8.035608657E9</v>
+      </c>
+      <c r="E65" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035608657</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3">
+        <v>8.035955362E9</v>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08035955362</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="3">
+        <v>8.036095254E9</v>
+      </c>
+      <c r="E67" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036095254</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>8.036101166E9</v>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036101166</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3">
+        <v>8.036154582E9</v>
+      </c>
+      <c r="E69" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036154582</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="3">
+        <v>8.036159011E9</v>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036159011</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3">
+        <v>8.036182252E9</v>
+      </c>
+      <c r="E71" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036182252</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="3">
+        <v>8.036225052E9</v>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036225052</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="3">
+        <v>8.036434589E9</v>
+      </c>
+      <c r="E73" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036434589</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="3">
+        <v>8.036437611E9</v>
+      </c>
+      <c r="E74" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036437611</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="3">
+        <v>8.036448843E9</v>
+      </c>
+      <c r="E75" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036448843</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="3">
+        <v>8.036478824E9</v>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036478824</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="3">
+        <v>8.036530551E9</v>
+      </c>
+      <c r="E77" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036530551</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="3">
+        <v>8.036739307E9</v>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036739307</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="3">
+        <v>8.036762719E9</v>
+      </c>
+      <c r="E79" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036762719</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="3">
+        <v>8.036780579E9</v>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036780579</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="3">
+        <v>8.036814333E9</v>
+      </c>
+      <c r="E81" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036814333</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="3">
+        <v>8.036974582E9</v>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036974582</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8.036981163E9</v>
+      </c>
+      <c r="E83" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08036981163</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="3">
+        <v>8.037123791E9</v>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037123791</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="3">
+        <v>8.037534931E9</v>
+      </c>
+      <c r="E85" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037534931</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8.037675008E9</v>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037675008</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="3">
+        <v>8.037726599E9</v>
+      </c>
+      <c r="E87" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037726599</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="3">
+        <v>8.037975591E9</v>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037975591</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="3">
+        <v>8.037987842E9</v>
+      </c>
+      <c r="E89" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08037987842</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="3">
+        <v>8.038020118E9</v>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038020118</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="3">
+        <v>8.038046445E9</v>
+      </c>
+      <c r="E91" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038046445</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="3">
+        <v>8.038083103E9</v>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038083103</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="3">
+        <v>8.038393287E9</v>
+      </c>
+      <c r="E93" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038393287</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="3">
+        <v>8.038393472E9</v>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038393472</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D95" s="3">
+        <v>8.03845951E9</v>
+      </c>
+      <c r="E95" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038459510</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="3">
+        <v>8.038485944E9</v>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038485944</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="3">
+        <v>8.03857238E9</v>
+      </c>
+      <c r="E97" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038572380</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="3">
+        <v>8.038583502E9</v>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038583502</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="3">
+        <v>8.038698474E9</v>
+      </c>
+      <c r="E99" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038698474</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="3">
+        <v>8.038833161E9</v>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08038833161</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3">
+        <v>8.039263258E9</v>
+      </c>
+      <c r="E101" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039263258</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D102" s="3">
+        <v>8.039281068E9</v>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039281068</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <v>8.039363846E9</v>
+      </c>
+      <c r="E2" s="4" t="str">
+        <f t="shared" ref="E2:E102" si="1">TEXT(D2,"00000000000")</f>
+        <v>08039363846</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.039375424E9</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039375424</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8.03940606E9</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039406060</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.039577458E9</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039577458</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.039664149E9</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039664149</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.039745691E9</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039745691</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.039805222E9</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08039805222</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.05036924E9</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08050369240</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.053392011E9</v>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08053392011</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8.053470032E9</v>
+      </c>
+      <c r="E11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08053470032</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.05448137E9</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08054481370</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.055941212E9</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08055941212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.056555154E9</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08056555154</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.05871448E9</v>
+      </c>
+      <c r="E15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08058714480</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.060293843E9</v>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060293843</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.060467948E9</v>
+      </c>
+      <c r="E17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060467948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8.060514643E9</v>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060514643</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8.060531062E9</v>
+      </c>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060531062</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8.060686058E9</v>
+      </c>
+      <c r="E20" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060686058</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.060837929E9</v>
+      </c>
+      <c r="E21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060837929</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8.060917351E9</v>
+      </c>
+      <c r="E22" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08060917351</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8.061120876E9</v>
+      </c>
+      <c r="E23" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061120876</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>8.061185168E9</v>
+      </c>
+      <c r="E24" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061185168</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>8.061335211E9</v>
+      </c>
+      <c r="E25" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061335211</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8.06137704E9</v>
+      </c>
+      <c r="E26" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061377040</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.061563973E9</v>
+      </c>
+      <c r="E27" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061563973</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>8.061578208E9</v>
+      </c>
+      <c r="E28" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061578208</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8.061677991E9</v>
+      </c>
+      <c r="E29" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08061677991</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>8.062271975E9</v>
+      </c>
+      <c r="E30" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062271975</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>8.062280247E9</v>
+      </c>
+      <c r="E31" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062280247</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.062498688E9</v>
+      </c>
+      <c r="E32" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062498688</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
+        <v>8.062500453E9</v>
+      </c>
+      <c r="E33" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062500453</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="3">
+        <v>8.062821377E9</v>
+      </c>
+      <c r="E34" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062821377</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>8.062896374E9</v>
+      </c>
+      <c r="E35" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08062896374</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3">
+        <v>8.063163318E9</v>
+      </c>
+      <c r="E36" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063163318</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3">
+        <v>8.06323334E9</v>
+      </c>
+      <c r="E37" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063233340</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="3">
+        <v>8.063449349E9</v>
+      </c>
+      <c r="E38" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063449349</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="3">
+        <v>8.063478441E9</v>
+      </c>
+      <c r="E39" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063478441</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8.063655834E9</v>
+      </c>
+      <c r="E40" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063655834</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3">
+        <v>8.063948199E9</v>
+      </c>
+      <c r="E41" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08063948199</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8.064018777E9</v>
+      </c>
+      <c r="E42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064018777</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8.064352408E9</v>
+      </c>
+      <c r="E43" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064352408</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="3">
+        <v>8.064458222E9</v>
+      </c>
+      <c r="E44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064458222</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="3">
+        <v>8.064610242E9</v>
+      </c>
+      <c r="E45" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064610242</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="3">
+        <v>8.064614497E9</v>
+      </c>
+      <c r="E46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064614497</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8.064813739E9</v>
+      </c>
+      <c r="E47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064813739</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>8.064815182E9</v>
+      </c>
+      <c r="E48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064815182</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="3">
+        <v>8.064853241E9</v>
+      </c>
+      <c r="E49" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08064853241</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3">
+        <v>8.065187539E9</v>
+      </c>
+      <c r="E50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065187539</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="3">
+        <v>8.065203666E9</v>
+      </c>
+      <c r="E51" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065203666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3">
+        <v>8.065225386E9</v>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065225386</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="3">
+        <v>8.065337508E9</v>
+      </c>
+      <c r="E53" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065337508</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3">
+        <v>8.065359017E9</v>
+      </c>
+      <c r="E54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065359017</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>8.065577335E9</v>
+      </c>
+      <c r="E55" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065577335</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>8.065587457E9</v>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065587457</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3">
+        <v>8.065724362E9</v>
+      </c>
+      <c r="E57" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065724362</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>8.065982363E9</v>
+      </c>
+      <c r="E58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065982363</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>8.06599601E9</v>
+      </c>
+      <c r="E59" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08065996010</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3">
+        <v>8.066083288E9</v>
+      </c>
+      <c r="E60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066083288</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3">
+        <v>8.066111463E9</v>
+      </c>
+      <c r="E61" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066111463</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3">
+        <v>8.066133971E9</v>
+      </c>
+      <c r="E62" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066133971</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>8.066173591E9</v>
+      </c>
+      <c r="E63" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066173591</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3">
+        <v>8.066254528E9</v>
+      </c>
+      <c r="E64" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066254528</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3">
+        <v>8.066331504E9</v>
+      </c>
+      <c r="E65" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066331504</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3">
+        <v>8.06641573E9</v>
+      </c>
+      <c r="E66" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08066415730</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="3">
+        <v>8.067217158E9</v>
+      </c>
+      <c r="E67" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067217158</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>8.067219378E9</v>
+      </c>
+      <c r="E68" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067219378</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3">
+        <v>8.067246146E9</v>
+      </c>
+      <c r="E69" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067246146</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="3">
+        <v>8.067342512E9</v>
+      </c>
+      <c r="E70" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067342512</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3">
+        <v>8.067361813E9</v>
+      </c>
+      <c r="E71" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067361813</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="3">
+        <v>8.067592868E9</v>
+      </c>
+      <c r="E72" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067592868</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="3">
+        <v>8.067637576E9</v>
+      </c>
+      <c r="E73" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08067637576</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="3">
+        <v>8.068089005E9</v>
+      </c>
+      <c r="E74" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068089005</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3">
+        <v>8.068207622E9</v>
+      </c>
+      <c r="E75" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068207622</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="3">
+        <v>8.068304053E9</v>
+      </c>
+      <c r="E76" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068304053</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="3">
+        <v>8.068387914E9</v>
+      </c>
+      <c r="E77" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068387914</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="3">
+        <v>8.068655324E9</v>
+      </c>
+      <c r="E78" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068655324</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="3">
+        <v>8.068767092E9</v>
+      </c>
+      <c r="E79" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068767092</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="3">
+        <v>8.068807767E9</v>
+      </c>
+      <c r="E80" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068807767</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="3">
+        <v>8.068830259E9</v>
+      </c>
+      <c r="E81" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08068830259</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="3">
+        <v>8.069039731E9</v>
+      </c>
+      <c r="E82" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069039731</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8.069233292E9</v>
+      </c>
+      <c r="E83" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069233292</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="3">
+        <v>8.069251992E9</v>
+      </c>
+      <c r="E84" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069251992</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="3">
+        <v>8.069449061E9</v>
+      </c>
+      <c r="E85" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069449061</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8.069521826E9</v>
+      </c>
+      <c r="E86" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069521826</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="3">
+        <v>8.069528282E9</v>
+      </c>
+      <c r="E87" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069528282</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="3">
+        <v>8.069686748E9</v>
+      </c>
+      <c r="E88" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069686748</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="3">
+        <v>8.069826487E9</v>
+      </c>
+      <c r="E89" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08069826487</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" s="3">
+        <v>8.071610698E9</v>
+      </c>
+      <c r="E90" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08071610698</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="3">
+        <v>8.072926406E9</v>
+      </c>
+      <c r="E91" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08072926406</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="3">
+        <v>8.073447998E9</v>
+      </c>
+      <c r="E92" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08073447998</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="3">
+        <v>8.077462851E9</v>
+      </c>
+      <c r="E93" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08077462851</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="3">
+        <v>8.080141531E9</v>
+      </c>
+      <c r="E94" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08080141531</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="3">
+        <v>8.080267153E9</v>
+      </c>
+      <c r="E95" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08080267153</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="3">
+        <v>8.080406007E9</v>
+      </c>
+      <c r="E96" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08080406007</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" s="3">
+        <v>8.080989217E9</v>
+      </c>
+      <c r="E97" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08080989217</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="3">
+        <v>8.081151169E9</v>
+      </c>
+      <c r="E98" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08081151169</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="3">
+        <v>8.081157169E9</v>
+      </c>
+      <c r="E99" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08081157169</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" s="3">
+        <v>8.081203068E9</v>
+      </c>
+      <c r="E100" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08081203068</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3">
+        <v>8.081530731E9</v>
+      </c>
+      <c r="E101" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08081530731</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="3">
+        <v>8.081643434E9</v>
+      </c>
+      <c r="E102" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>08081643434</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>